--- a/smartshop/EvidenceBasedAdaptiveUI/reports/AdaptiveDecisionEngine/simulation_results.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/AdaptiveDecisionEngine/simulation_results.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
         <v>28</v>
@@ -554,17 +554,17 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
         <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Cool Blues", "filter_location": "Top Bar", "font_style": "Rounded Friendly", "form_field": "Rounded Border Fields", "grid_layout": "2 Columns", "hero_banner": "Medium Split", "information_density": "-3", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "With Comparison", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "0", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Cool Blues", "filter_location": "Top Bar", "font_style": "Rounded Friendly", "form_field": "Rounded Border Fields", "grid_layout": "4 Columns", "hero_banner": "Medium Split", "information_density": "-3", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "With Comparison", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -624,11 +624,11 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "One Page", "color_theme": "Vibrant Bold", "filter_location": "Sidebar Left", "font_style": "Modern Sans-serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Large Full screen", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "All Paginated", "search_visibility": "Always Visible Top", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "None", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "One Page", "color_theme": "Vibrant Bold", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "2 Columns", "hero_banner": "Large Full screen", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "All Paginated", "search_visibility": "Always Visible Top", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "None", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "+1"}</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -665,34 +665,34 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>global + device</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>global + device</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "One Page", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Rounded Border Fields", "grid_layout": "4 Columns", "hero_banner": "Large Full screen", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Stock Numbers", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Cool Blues", "filter_location": "Top Bar", "font_style": "Classic Serif", "form_field": "Rounded Border Fields", "grid_layout": "3 Columns", "hero_banner": "Large Full screen", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Compact", "navigation": "Sidebar", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Recent 3- 5", "search_visibility": "Always Visible Top", "social_proof": "Bestseller Badges", "typography_scale": "Large", "urgency": "Stock Numbers", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "-1"}</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -738,7 +738,7 @@
         <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "Progress Bar", "color_theme": "Cool Blues", "filter_location": "Bottom Sheet", "font_style": "Rounded Friendly", "form_field": "Rounded Border Fields", "grid_layout": "Compact stacked cards", "hero_banner": "Small Strip", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Stock Numbers", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Light Gray", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "Progress Bar", "color_theme": "Cool Blues", "filter_location": "Bottom Sheet", "font_style": "Rounded Friendly", "form_field": "Rounded Border Fields", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "+1"}</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>27</v>
@@ -810,17 +810,17 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Medium Split", "information_density": "+1", "information_density_level": "Detailed", "layout_whitespace": "Balanced", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Moderate", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "0", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Medium Split", "information_density": "+1", "information_density_level": "Detailed", "layout_whitespace": "Balanced", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Recent 3- 5", "search_visibility": "Always Visible Top", "social_proof": "Customer Reviews", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "0", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>32</v>
@@ -874,17 +874,17 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Small Strip", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Moderate", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Small Strip", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Compact", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "No", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "-1"}</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Dark", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "One Page", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Rounded Friendly", "form_field": "Rounded Border Fields", "grid_layout": "Compact stacked cards", "hero_banner": "None", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Spacious", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Detailed Full", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Summary Only", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Dark", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "One Page", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Rounded Friendly", "form_field": "Filled Background", "grid_layout": "Compact stacked cards", "hero_banner": "None", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Spacious", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Summary Only", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "+1"}</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "One Page", "color_theme": "Vibrant Bold", "filter_location": "Drawer Overlay", "font_style": "Modern Sans-serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Small Strip", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "No", "touch_size": "Standard", "typography_scale": "Large", "urgency": "None", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "One Page", "color_theme": "Vibrant Bold", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Small Strip", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "Customer Reviews", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "None", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -1122,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>6</v>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Moderate", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1250,7 +1250,7 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Vibrant Bold", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Filled Background", "grid_layout": "Compact stacked cards", "hero_banner": "Large Full screen", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Category based", "recommendation_strength": "-1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "Customer Reviews", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Vibrant Bold", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Filled Background", "grid_layout": "Compact stacked cards", "hero_banner": "Large Full screen", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Category based", "recommendation_strength": "-1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "Customer Reviews", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>28</v>
@@ -1322,17 +1322,17 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Medium Split", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Moderate", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Medium Split", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Compact", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Recent 3- 5", "search_visibility": "Always Visible Top", "social_proof": "Customer Reviews", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "-1"}</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Dark", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "One Page", "color_theme": "Cool Blues", "filter_location": "Drawer Overlay", "font_style": "Rounded Friendly", "form_field": "Rounded Border Fields", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Info Rich", "product_description": "Detailed Full", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Summary Only", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Dark", "button_style": "Rounded Corners", "category_display": "Dropdown Menu", "checkout": "One Page", "color_theme": "Warm Earthy", "filter_location": "Drawer Overlay", "font_style": "Rounded Friendly", "form_field": "Filled Background", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Summary Only", "search_visibility": "Collapsible", "social_proof": "Customer Reviews", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1450,17 +1450,17 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Minimalist Black &amp; White", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Rounded Border Fields", "grid_layout": "Compact stacked cards", "hero_banner": "Large Full screen", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "Customer Reviews", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Minimalist Black &amp; White", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Rounded Border Fields", "grid_layout": "Compact stacked cards", "hero_banner": "Large Full screen", "information_density": "-1", "information_density_level": "Minimal", "layout_whitespace": "Compact", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "Bestseller Badges", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "-1"}</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "One Page", "color_theme": "Minimalist Black &amp; White", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Rounded Border Fields", "grid_layout": "List View", "hero_banner": "None", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "Customer Reviews", "typography_scale": "Large", "urgency": "Stock Numbers", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Light Gray", "button_style": "Rounded Corners", "category_display": "Text List", "checkout": "Progress Bar", "color_theme": "Minimalist Black &amp; White", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Rounded Border Fields", "grid_layout": "3 Columns", "hero_banner": "Small Strip", "information_density": "0", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "-1", "review_display": "Recent 3- 5", "search_visibility": "Always Visible Top", "social_proof": "Bestseller Badges", "typography_scale": "Large", "urgency": "Countdown Timers", "visual_balance": "Text-focused", "visual_richness": "-1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>27</v>
@@ -1584,11 +1584,11 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Vibrant Bold", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Filled Background", "grid_layout": "3 Columns", "hero_banner": "Small Strip", "information_density": "-1", "information_density_level": "Moderate", "layout_whitespace": "Spacious", "navigation": "Combination of top bar and dropdowns", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Category based", "recommendation_strength": "+1", "review_display": "All Paginated", "search_visibility": "Always Visible Top", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Balanced", "visual_richness": "-1", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Vibrant Bold", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Filled Background", "grid_layout": "3 Columns", "hero_banner": "Small Strip", "information_density": "-1", "information_density_level": "Moderate", "layout_whitespace": "Balanced", "navigation": "Combination of top bar and dropdowns", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Category based", "recommendation_strength": "0", "review_display": "All Paginated", "search_visibility": "Always Visible Top", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Balanced", "visual_richness": "-1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
@@ -1642,17 +1642,17 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "4 Columns", "hero_banner": "Large Full screen", "information_density": "+1", "information_density_level": "Detailed", "layout_whitespace": "Balanced", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Info Rich", "product_description": "Moderate", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Stock Numbers", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Cool Blues", "filter_location": "Top Bar", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Large Full screen", "information_density": "+1", "information_density_level": "Detailed", "layout_whitespace": "Balanced", "navigation": "Sidebar", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Always Visible Top", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Stock Numbers", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1692,13 +1692,13 @@
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1709,14 +1709,14 @@
         <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
         <v>7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Vibrant Bold", "filter_location": "Drawer Overlay", "font_style": "Modern Sans-serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "-2", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "No", "touch_size": "Standard", "typography_scale": "Large", "urgency": "None", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Vibrant Bold", "filter_location": "Drawer Overlay", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "Compact stacked cards", "hero_banner": "Medium Split", "information_density": "-2", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Bottom Nav", "price_display": "Strike-through Original", "product_card": "Minimal Clean", "product_description": "Expandable Sections", "quick_view": "Slide-Up Panel", "recommendation": "Deals", "recommendation_strength": "+1", "review_display": "Collapsible Sections", "search_visibility": "Collapsible", "social_proof": "User Photos", "sticky_header": "Yes", "touch_size": "Standard", "typography_scale": "Large", "urgency": "None", "visual_balance": "Balanced", "visual_richness": "0", "whitespace": "+1"}</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
         <v>27</v>
@@ -1770,17 +1770,17 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Large Full screen", "information_density": "-2", "information_density_level": "Minimal", "layout_whitespace": "Spacious", "navigation": "Mega Menu", "persistent_filters": "Yes", "price_display": "With Savings Highlighted", "product_card": "Info Rich", "product_description": "Moderate", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Collapsible", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "+1"}</t>
+          <t>{"accent_color": "Blue", "animation": "0", "background": "Cream/Off-white", "button_style": "Rounded Corners", "category_display": "Visual Grid", "checkout": "Progress Bar", "color_theme": "Warm Earthy", "filter_location": "Sidebar Left", "font_style": "Classic Serif", "form_field": "Outlined", "grid_layout": "3 Columns", "hero_banner": "Large Full screen", "information_density": "-2", "information_density_level": "Minimal", "layout_whitespace": "Balanced", "navigation": "Top Bar", "persistent_filters": "Yes", "price_display": "Bold Large", "product_card": "Info Rich", "product_description": "Expandable Sections", "quick_view": "Sidebar Slide", "recommendation": "Deals", "recommendation_strength": "0", "review_display": "Recent 3- 5", "search_visibility": "Always Visible Top", "social_proof": "User Photos", "typography_scale": "Large", "urgency": "Both", "visual_balance": "Image-focused", "visual_richness": "+1", "whitespace": "0"}</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Top Bar (Filters displayed across the top)</t>
+          <t>Sidebar Left (Permanent filter panel on the left side)</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1. Modern Sans-serif (Clean, contemporary fonts like Arial or Helvetica)</t>
+          <t>2. Classic Serif (Traditional fonts with decorative strokes like Times New Roman)</t>
         </is>
       </c>
     </row>
@@ -2097,70 +2097,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>product_desc_length</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>No (Header scrolls away with content)</t>
+          <t>Expandable Sections (Organized into collapsible sections)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>product_desc_length</t>
+          <t>recommendation_type</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expandable Sections (Organized into collapsible sections)</t>
+          <t>Deals (Products on sale or special offers)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>recommendation_type</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deals (Products on sale or special offers)</t>
+          <t>Customer Reviews (Written reviews with ratings)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>social_proof_display</t>
+          <t>urgency_pref</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Customer Reviews (Written reviews with ratings)</t>
+          <t>Countdown Timers (Show "Sale ends in 2 hours")</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>whitespace_pref</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
-        <is>
-          <t>None (I find these annoying and manipulative)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>whitespace_pref</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
         <is>
           <t>Balanced (Moderate spacing - comfortable middle ground)</t>
         </is>
@@ -2284,7 +2272,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Top Bar</t>
+          <t>Sidebar Left</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2284,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modern Sans-serif</t>
+          <t>Classic Serif</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2512,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Countdown Timers</t>
         </is>
       </c>
     </row>
